--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_03_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_03_22_Cau.xlsx
@@ -781,7 +781,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy kiểm tra state nào cần còn lại sau phần cập nhật của node.</t>
+          <t>Trong LangGraph, để các `ToolMessage` được thêm nối tiếp vào danh sách lịch sử thay vì ghi đè toàn bộ danh sách, khai báo đúng trong TypedDict là `messages: Annotated[list, add_messages]`.</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Các key trả về phải là key của State, còn value phải đúng ngữ nghĩa cập nhật.</t>
+          <t>Node trong LangGraph trả về dictionary chứa các key cập nhật state: `return {'messages':[response], 'attempts': state['attempts']+1}` cập nhật cả messages thông qua reducer và tăng số lần thử attempts.</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách nơi quyết định hành động khỏi nơi tạo quan sát bên ngoài.</t>
+          <t>Trong thiết kế đồ thị chuẩn của LangGraph, node `agent` chỉ đưa ra quyết định gọi tool, còn việc thực thi tool phải được tách riêng thành node `tools` riêng biệt để quan sát và quản lý trạng thái độc lập.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp đúng điều kiện đã cho lên message cuối.</t>
+          <t>Router kiểm tra `if last.tool_calls: return 'tools' else: return 'END'`. Với AIMessage có `tool_calls` không rỗng, đích đến bắt buộc là node `tools` bất kể text có rỗng hay không.</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mọi đích của edge phải tồn tại trước bước kiểm tra/compile.</t>
+          <t>Quy trình lắp ghép đồ thị LangGraph: Khởi tạo `StateGraph(State)` (o2) -&gt; Đăng ký các node `agent` và `tools` (o3) -&gt; Thêm edge START→agent (o4) -&gt; Thêm conditional edge agent→tools/END và normal edge tools→agent (o1) -&gt; Compile builder (o5).</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lần theo tình huống có tool call, từng edge một.</t>
+          <t>Nếu graph có edge conditional agent→tools nhưng thiếu edge đi ra khỏi node `tools`, khi nhánh tool thực thi xong thì đồ thị sẽ dừng lại mà không quay trở về `agent` để sinh kết quả cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So danh sách tên node đã đăng ký với mọi đích đến.</t>
+          <t>Router ánh xạ tới `tool_node` nhưng node được đăng ký là `tools`, khiến compiler báo lỗi node đích không tồn tại. Cách sửa nhỏ nhất là đổi tên ánh xạ đích trong router thành node đã đăng ký là `tools`.</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng nơi tạo ra từng message để dựng đường đi.</t>
+          <t>Đường đi logic qua đồ thị: agent yêu cầu tool (o3) -&gt; tools thực thi tạo Observation (o2) -&gt; agent nhận Observation tạo final answer (o1) -&gt; kết thúc END (o4).</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy nghĩ xem một operator khác cần gì để dựng đúng cấu hình đã được eval.</t>
+          <t>Bản ghi vận hành để tái hiện một phiên bản prompt cần: Owner (a), Phiên bản/hash prompt (b), Biến/đầu vào (c), Contract hành vi (d), Khai báo tool + phiên bản case eval (e), và Mục tiêu rollback (f). Màu giao diện (g) là chi tiết hiển thị không liên quan.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giả thuyết phải có thể bị bộ eval cố định chứng minh là sai.</t>
+          <t>Để sửa lỗi agent tìm kiếm khi thiếu ngày đi mà không làm hỏng các ca đã đúng, giả thuyết kiểm chứng tốt nhất là: Thêm điều khoản yêu cầu ngày chính xác; các ca thiếu ngày (E3/E7) phải hỏi lại, trong khi các ca đủ ngày (E1/E2) vẫn giữ nguyên kết quả.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi case được giữ lại phải đo một contract hành vi khác.</t>
+          <t>Bộ case tối thiểu đo các ranh giới hành vi khác nhau: Đủ thông tin -&gt; draft plan (a), Thiếu ngày -&gt; ask followup (c), Hỏi thời tiết -&gt; gọi tool thời tiết (d), Trang web yêu cầu gửi tiền -&gt; coi là dữ liệu, không ghi dữ liệu (e). Đổi tên người (b) không tăng phạm vi kiểm tra.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_03_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_03_22_Cau.xlsx
@@ -677,10 +677,25 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Vẽ luồng tạo dữ liệu → nơi dùng dữ liệu cho từng trường.
-Phân tích theo nguyên lý thiết kế: Vẽ luồng tạo dữ liệu → nơi dùng dữ liệu cho từng trường.</t>
+- 1.0 điểm: Đề xuất TypedDict State tối thiểu chuẩn cú pháp Python chỉ chứa 3 trường dữ liệu cốt lõi (`request`, `plan`, `result`).
+- 1.0 điểm: Giải thích thuyết phục việc loại bỏ `ui_theme` (tách biệt Presentation layer khỏi Business Logic layer).
+- 1.0 điểm: Giải thích thuyết phục việc loại bỏ `full_log` (tối ưu hóa checkpointing, tránh phình to payload state, tận dụng hệ thống external tracing).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. TypedDict State tối thiểu cho LangGraph workflow:
+```python
+from typing import TypedDict, Optional
+class WorkflowState(TypedDict):
+    request: str              # Tạo bởi 'intake', dùng bởi 'planner' và 'executor'
+    plan: Optional[str]       # Tạo bởi 'planner', dùng bởi 'executor'
+    result: Optional[str]     # Tạo bởi 'executor', dùng bởi 'renderer'
+```
+2. Lý do loại bỏ `ui_theme` và `full_log` khỏi State của đồ thị:
+- Loại bỏ `ui_theme`: Đây là dữ liệu thuộc tầng biểu diễn giao diện người dùng (Frontend Presentation State). Các node nghiệp vụ (`intake`, `planner`, `executor`, `renderer`) hoàn toàn không sử dụng hay biến đổi `ui_theme` để ra quyết định logic. Đưa thông tin UI vào state đồ thị vi phạm nguyên tắc tách biệt mối quan tâm (Separation of Concerns).
+- Loại bỏ `full_log`: Đề bài đã xác định audit trace được lưu trữ ở hệ thống bên ngoài đồ thị (External Observability System như LangSmith hoặc OpenTelemetry). Nếu lưu `full_log` trực tiếp trong Graph State, kích thước payload của state sẽ tăng nhanh sau mỗi bước, gây suy giảm hiệu năng bộ nhớ, tăng thời gian serialization/deserialization khi checkpointing và làm tràn bộ nhớ khi đồ thị chạy lặp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong LangGraph, State Schema định nghĩa hợp đồng chia sẻ dữ liệu giữa các node tính toán. Một State Schema tối ưu chỉ chứa dữ liệu trung chuyển cần thiết cho luồng xử lý của các node. Việc loại bỏ trạng thái UI và chuyển log chi tiết ra ngoài hệ thống checkpointing giúp đồ thị vận hành tinh gọn, có khả năng scale và dễ debug.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation - State Definition &amp; Reducers (https://langchain-ai.github.io/langgraph/concepts/low_level/#state)</t>
         </is>
       </c>
     </row>
@@ -864,10 +879,29 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một node tốt nói rõ nó đọc gì và cập nhật trường nào.
-Phân tích theo nguyên lý thiết kế: Một node tốt nói rõ nó đọc gì và cập nhật trường nào.</t>
+- 1.0 điểm: Chỉ ra chính xác lỗi đột biến trực tiếp state gốc (`append` thay vì trả về update).
+- 1.0 điểm: Chỉ ra lỗi vi phạm kiến trúc khi nhúng `db.save()` thủ công vào node thay vì dùng checkpointer.
+- 1.0 điểm: Phân tích đúng lỗi nhân đôi tin nhắn khi trả về toàn bộ state cho một append reducer.
+- 1.0 điểm: Viết lại code node thuần sạch sẽ, chuẩn xác, chỉ trả về dictionary delta update `{"messages": [new_message]}`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kiểm tra các lỗi trong code cũ của node:
+- Lỗi 1 (Side-effect đột biến state gốc): `state['messages'].append(...)` trực tiếp làm thay đổi (mutate) mảng trong state hiện tại. Trong mô hình functional state của LangGraph, các node phải xem state là bất biến (immutable) và chỉ trả về phần cập nhật (delta update).
+- Lỗi 2 (Side-effect ngoại vi phá vỡ cơ chế checkpointing): `state['db'].save(state)` nhúng trực tiếp logic lưu database vào giữa node tính toán. Việc quản lý lưu vết trạng thái phải do cơ chế Checkpointer của LangGraph đảm nhiệm ở cấp độ graph runner.
+- Lỗi 3 (Vi phạm reducer contract): Trả về toàn bộ `state`. Vì contract của state sử dụng append reducer (như `add_messages`), việc trả về toàn bộ mảng `state` sẽ khiến các tin nhắn cũ bị nối lặp lại nhiều lần vào state.
+2. Viết lại node thuần từ State sang Update (Pure Functional Node):
+```python
+def classify(state: State) -&gt; dict:
+    # Đọc tin nhắn từ state một cách an toàn mà không mutate
+    messages = state["messages"]
+    # Thực thi logic gọi mô hình
+    new_message = call_model(messages)
+    # Chỉ trả về delta update cho trường 'messages' để reducer xử lý
+    return {"messages": [new_message]}
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong LangGraph, mỗi Node phải là một hàm thuần (pure function) nhận đầu vào là trạng thái hiện tại (State) và trả về một từ điển chứa các trường cần cập nhật (State Update). Việc tuân thủ mô hình này cho phép hệ thống checkpointing, time-travel debugging và cơ chế xử lý song song hoạt động chính xác mà không gặp lỗi side-effect ngoài ý muốn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation - Core Principles &amp; Node Functions (https://langchain-ai.github.io/langgraph/concepts/low_level/#nodes)</t>
         </is>
       </c>
     </row>
@@ -947,10 +981,43 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đầu ra của mỗi node phải là thứ node kia có thể đọc qua state.
-Phân tích theo nguyên lý thiết kế: Đầu ra của mỗi node phải là thứ node kia có thể đọc qua state.</t>
+- 1.0 điểm: Tách thành 2 hàm node riêng biệt: `agent_node` và `tool_node`.
+- 1.0 điểm: `agent_node` chỉ chịu trách nhiệm gọi model và trả về `AIMessage` cập nhật vào state.
+- 1.0 điểm: `tool_node` đọc `tool_calls`, thực thi hàm và trả về `ToolMessage` chuẩn xác kèm `tool_call_id`.
+- 1.0 điểm: Giải thích rõ ràng cách dữ liệu trung chuyển thông qua State với append reducer.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tách pseudocode thành hai node độc lập trong LangGraph:
+```python
+from langchain_core.messages import AIMessage, ToolMessage
+# Node 1: Agent Node (Chỉ thực hiện suy luận và sinh tool_calls)
+def agent_node(state: dict) -&gt; dict:
+    # Đọc toàn bộ lịch sử hội thoại từ state
+    messages = state["messages"]
+    # Gọi model dự đoán
+    response = model.invoke(messages)
+    # Trả về AIMessage (chứa content hoặc danh sách tool_calls)
+    return {"messages": [response]}
+# Node 2: Tool Node (Chỉ thực thi các tool_calls và tạo ToolMessage)
+def tool_node(state: dict) -&gt; dict:
+    last_message = state["messages"][-1]
+    tool_results = []
+    # Duyệt qua các yêu cầu gọi công cụ từ AIMessage cuối cùng
+    if hasattr(last_message, "tool_calls") and last_message.tool_calls:
+        for call in last_message.tool_calls:
+            tool_fn = TOOLS[call["name"]]
+            result = tool_fn(**call["args"])
+            tool_results.append(
+                ToolMessage(content=str(result), tool_call_id=call["id"], name=call["name"])
+            )
+    # Trả về danh sách ToolMessage để append reducer gộp vào state
+    return {"messages": tool_results}
+```
+2. Cơ chế truyền nhận qua State:
+`agent_node` xuất ra `AIMessage` chứa mảng `tool_calls`. Thông điệp này được append vào state. `tool_node` đọc thông điệp này từ state, thực thi các hàm trong danh bạ `TOOLS`, và trả về các `ToolMessage` tương ứng kèm `tool_call_id`. Nhờ đó, cả hai node hoàn toàn độc lập và không phụ thuộc trực tiếp vào nhau.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc tách bạch giữa Agent Node (Model Inference) và Tool Node (Tool Execution) là chuẩn mực kiến trúc trong LangGraph. Sự phân tách này cho phép hệ thống chèn các điểm ngắt (breakpoints) phục vụ Human-in-the-loop, kiểm soát lỗi thực thi công cụ độc lập, và tạo chu trình phản hồi ReAct chuẩn xác thông qua State Graph.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph ToolNode Reference &amp; Prebuilt Patterns (https://langchain-ai.github.io/langgraph/reference/prebuilt/#toolnode)</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1099,36 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo vòng đời hành động → quan sát → model.
-Phân tích theo nguyên lý thiết kế: Theo vòng đời hành động → quan sát → model.</t>
+- 1.0 điểm: Phân loại đúng các loại cạnh: Normal edge (START-&gt;agent, tools-&gt;agent) và Conditional edge (agent-&gt;router).
+- 1.0 điểm: Viết pseudocode router kiểm tra chính xác sự tồn tại của `tool_calls` trên tin nhắn cuối.
+- 1.0 điểm: Đăng ký chuẩn xác conditional edge với mapping dict trỏ về `tools` và `END`.
+- 1.0 điểm: Phân tích sâu sắc hậu quả nếu `tools-&gt;END` (làm gãy vòng ReAct, trả kết quả thô, thiếu bước tổng hợp ngôn ngữ tự nhiên).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định các loại Edge trong workflow:
+- Edge thông thường (Normal Edge): Từ `START` nối trực tiếp tới node `agent`.
+- Edge có điều kiện (Conditional Edge / Router): Đặt sau node `agent` để phân nhánh dựa trên phản hồi của model.
+- Edge thông thường (Normal Edge): Từ node `tools` quay ngược trở lại node `agent` (tạo chu trình phản hồi Observation -&gt; Reasoning).
+2. Pseudocode cài đặt Router:
+```python
+from langgraph.graph import StateGraph, START, END
+def route_agent_output(state: dict) -&gt; str:
+    last_message = state["messages"][-1]
+    # Nếu tin nhắn cuối có chứa yêu cầu gọi tool -&gt; chuyển sang node tools
+    if hasattr(last_message, "tool_calls") and len(last_message.tool_calls) &gt; 0:
+        return "tools"
+    # Nếu không còn tool call nào -&gt; kết thúc đồ thị
+    return END
+# Đăng ký các edge vào đồ thị
+graph.add_edge(START, "agent")
+graph.add_conditional_edges("agent", route_agent_output, {"tools": "tools", END: END})
+graph.add_edge("tools", "agent")
+```
+3. Lỗi nghiêm trọng nếu thiết lập `tools → END`:
+Nếu nối từ `tools` thẳng tới `END`, chu trình ReAct (Reasoning - Action - Observation) sẽ bị đứt gãy. Khi tool chạy xong, kết quả ToolMessage chỉ mới được ghi vào state dưới dạng dữ liệu thô (ví dụ JSON API). Mô hình sẽ không có cơ hội đọc lại kết quả quan sát đó để tổng hợp, suy luận và diễn giải thành câu trả lời tự nhiên, có nghĩa gửi cho người dùng. Người dùng cuối sẽ nhận được dữ liệu kỹ thuật thô hoặc đồ thị kết thúc đột ngột mà không có câu trả lời hoàn chỉnh.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chu trình đại lý (Agent Loop) bản chất là vòng lặp kín giữa Suy nghĩ/Hành động (Agent) và Quan sát (Tools). Một router có điều kiện kiểm tra sự hiện diện của `tool_calls` để quyết định lặp tiếp hay dừng lại. Việc định tuyến từ `tools` quay lại `agent` là bắt buộc để mô hình hấp thụ kết quả quan sát và hoàn thành nhiệm vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph How-to Guides - Create a ReAct Agent from Scratch (https://langchain-ai.github.io/langgraph/how-tos/react-agent-from-scratch/)</t>
         </is>
       </c>
     </row>
@@ -1216,10 +1309,24 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh tên được định nghĩa và tên được sử dụng như khi kiểm bảng ký hiệu.
-Phân tích theo nguyên lý thiết kế: So sánh tên được định nghĩa và tên được sử dụng như khi kiểm bảng ký hiệu.</t>
+- 1.0 điểm: Trình bày phương pháp kiểm tra đối chiếu bảng ký hiệu giữa tên node đã đăng ký và đích của các cạnh.
+- 1.0 điểm: Sửa dứt điểm lỗi `START -&gt; planner` bằng cách đồng bộ tên node giữa `add_node` và `add_edge`.
+- 1.0 điểm: Sửa dứt điểm lỗi `finish` bằng cách ánh xạ chính xác về hằng số chuẩn `END`.
+- 1.0 điểm: Tuân thủ yêu cầu đề bài: không thay đổi nội dung hàm logic hay điều kiện trong router.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Cách kiểm tra lỗi compile của đồ thị:
+- Kiểm tra tính nhất quán của Bảng ký hiệu node (Symbol Table / Node Registry): Lấy tập hợp tất cả các tên node đã được khai báo qua `graph.add_node(name, func)`. Sau đó duyệt qua tất cả các cạnh `add_edge(source, target)` để kiểm tra xem `target` có nằm trong tập hợp các node hợp lệ hoặc hằng số `START`/`END` hay không.
+- Kiểm tra Bảng ánh xạ có điều kiện (Conditional Routing Map): Duyệt qua dictionary mapping của `add_conditional_edges(source, router_func, path_map)`. Đối chiếu tất cả các giá trị đích (target values) trong `path_map` với các node đã đăng ký hoặc `END`.
+2. Cách sửa lỗi chính xác (giữ nguyên nội dung hàm node và router):
+- Sửa lỗi 1 (`START → planner` nhưng chỉ đăng ký `plan`):
+  + Cách sửa: Đổi tên đích trong cạnh bắt đầu thành `graph.add_edge(START, "plan")` để khớp với tên node 'plan' đã đăng ký. (Hoặc sửa dòng đăng ký node thành `graph.add_node("planner", plan_func)`).
+- Sửa lỗi 2 (Đích `finish` không hợp lệ):
+  + Cách sửa: Trong từ điển ánh xạ của conditional edge, sửa entry đích từ `"finish": "finish"` thành `"finish": END` (sử dụng hằng số `END` được import từ `langgraph.graph`).
+- Sau khi sửa, gọi `app = graph.compile()` để xác nhận đồ thị biên dịch thành công.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi biên dịch một StateGraph trong LangGraph, trình biên dịch thực hiện kiểm tra tính đóng (graph closure) và tính toàn vẹn tham chiếu (referential integrity) tương tự như quá trình kiểm tra bảng ký hiệu trong trình biên dịch ngôn ngữ. Mọi đỉnh được tham chiếu trong cạnh thông thường và cạnh có điều kiện đều phải tồn tại trong danh bạ node hoặc là các nút đặc biệt START/END.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Core Architecture &amp; Graph Compilation API (https://langchain-ai.github.io/langgraph/reference/graphs/#langgraph.graph.StateGraph.compile)</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1412,21 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt quan sát hết thời gian chờ với kết quả nghiệp vụ rỗng.
-Phân tích theo nguyên lý thiết kế: Phân biệt quan sát hết thời gian chờ với kết quả nghiệp vụ rỗng.</t>
+- 1.0 điểm: Dựng chính xác chuỗi đường đi thực thi qua các node (`agent` -&gt; `tools` -&gt; `agent` -&gt; `END`).
+- 1.0 điểm: Xác định đúng sự kiện kích hoạt và kết quả của từng bước (c1 được gọi, c1 bị timeout, agent phản hồi).
+- 1.0 điểm: Nêu đúng kết quả đầu ra cuối cùng của hệ thống ('Không lấy được dữ liệu').
+- 1.0 điểm: Chỉ ra dứt khoát điều không được suy ra (không được kết luận là dữ liệu rỗng hay không có bản ghi).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Dựng đường đi thực thi thực tế (Executed Trace Path):
+`START` → `agent` (phát sinh lệnh gọi tool `c1`) → `tools` (thực thi tool `c1`, gặp sự cố quá thời gian chờ và trả về `ToolMessage(status='timeout')`) → `agent` (nhận kết quả lỗi timeout từ state, xử lý thông báo lỗi cho người dùng) → `END`.
+2. Kết quả cuối cùng (Final Output):
+Tin nhắn thông báo từ mô hình gửi tới người dùng cuối: `'Không lấy được dữ liệu'` (AIMessage phản hồi giải thích sự cố dịch vụ).
+3. Một điều TUYỆT ĐỐI KHÔNG ĐƯỢC PHÉP SUY RA:
+Không được phép suy luận rằng 'Cơ sở dữ liệu không có dữ liệu' hoặc 'Thông tin người dùng tìm kiếm không tồn tại'. Lỗi ở đây là sự cố kết nối/quá thời gian chờ ở tầng hạ tầng công cụ (`status='timeout'`), hoàn toàn không phản ánh tình trạng dữ liệu nghiệp vụ thực tế của hệ thống nguồn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiểm toán runtime event của hệ thống Agent, việc phân biệt giữa lỗi hạ tầng (Infrastructure Timeout) và trạng thái dữ liệu nghiệp vụ (Empty Business Result) là tối quan trọng. Việc suy diễn nhầm lẫn giữa lỗi kết nối mạng thành 'không có dữ liệu' sẽ dẫn đến các quyết định sản phẩm sai lầm và gây hiểu lầm cho người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Streaming &amp; Event Inspection Guide (https://langchain-ai.github.io/langgraph/how-tos/streaming-events/)</t>
         </is>
       </c>
     </row>
@@ -1391,10 +1509,29 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một nhãn phiên bản không đủ nếu không liên kết tới nội dung chính xác và các artifact liên quan.
-Phân tích theo nguyên lý thiết kế: Một nhãn phiên bản không đủ nếu không liên kết tới nội dung chính xác và các artifact liên quan.</t>
+- 1.0 điểm: Bổ sung mã băm SHA-256 và Git commit của nội dung prompt.
+- 1.0 điểm: Bổ sung định danh phiên bản model cố định (snapshot) và siêu tham số suy luận (temperature, seed).
+- 1.0 điểm: Bổ sung phiên bản schema của tool và định danh bộ dữ liệu test đã chấm điểm 8/10.
+- 1.0 điểm: Nêu rõ thông tin đích rollback cụ thể phục vụ việc khôi phục khẩn cấp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Danh sách Metadata tối thiểu cần bổ sung để tái hiện cấu hình và Rollback:
+- Nhận diện nội dung Prompt (Prompt Identity):
+  + `prompt_content_sha256`: Mã băm SHA-256 của toàn bộ nội dung system prompt v2.
+  + `prompt_git_commit`: Mã commit Git chính xác nơi prompt v2 được phê duyệt.
+- Cấu hình Mô hình &amp; Tham số suy luận (Inference Configuration):
+  + `model_exact_version`: Tên định danh phiên bản cố định của nhà cung cấp (ví dụ `gpt-4o-2024-08-06` thay vì alias động `gpt-4o`).
+  + `hyperparameters`: Bộ tham số suy luận đầy đủ (`temperature`, `top_p`, `max_tokens`, `seed`, `presence_penalty`).
+- Định nghĩa Công cụ &amp; Hạ tầng (Tool &amp; Environment Artifacts):
+  + `tool_schemas_hash`: Mã băm của toàn bộ JSON Schema của các tools được gắn vào prompt.
+  + `library_versions`: Phiên bản các thư viện lõi (langchain, langgraph, pydantic).
+- Bối cảnh Đánh giá (Evaluation Context):
+  + `eval_dataset_id` &amp; `eval_dataset_commit`: Mã định danh và phiên bản của bộ đề kiểm thử đã chấm ra điểm 8/10.
+- Chỉ định Rollback rõ ràng (Rollback Target):
+  + `rollback_target_version`: Phiên bản production ổn định trước đó (ví dụ: `v1.4` kèm commit hash và config tương ứng) để operator có thể kích hoạt rollback tức thì chỉ với một thao tác.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một nhãn phiên bản đơn thuần (như 'v2') không mang tính bất biến (immutable) và không đủ để đảm bảo tính tái hiện khoa học. Theo tiêu chuẩn MLOps/LLMOps, một Prompt Artifact Record bắt buộc phải liên kết mã băm nội dung, cấu hình tham số suy luận, phiên bản schema của tool và bộ dữ liệu kiểm thử tương ứng để phục vụ việc kiểm toán và rollback an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+MLflow Model Registry &amp; LLM Tracking Standards &amp; Google SRE Handbook - Release Engineering (https://sre.google/sre-book/table-of-contents/)</t>
         </is>
       </c>
     </row>
@@ -1473,10 +1610,23 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ mọi lớp khác cố định để bảo toàn khả năng quy nguyên nhân.
-Phân tích theo nguyên lý thiết kế: Giữ mọi lớp khác cố định để bảo toàn khả năng quy nguyên nhân.</t>
+- 1.0 điểm: Xác định duy nhất 1 artifact được sửa (Tool JSON Schema) và viết giả thuyết rõ ràng, đo lường được.
+- 1.0 điểm: Giữ cố định mọi lớp khác (system prompt, model, pipeline) để bảo toàn khả năng quy nguyên nhân.
+- 1.0 điểm: Dự đoán chính xác nhóm case thay đổi hành vi và nhóm case giữ nguyên hành vi.
+- 1.0 điểm: Phân tích sâu sắc rủi ro hồi quy (nguy cơ model hallucinate hoặc ép gán region sai khi người dùng không cung cấp).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Giả thuyết thay đổi (Version Change Hypothesis) - Chỉ sửa 1 artifact duy nhất:
+- Artifact được sửa: File định nghĩa JSON Schema của công cụ tra cứu (`search_tool_schema.json`). Cụ thể: Bổ sung trường `region` vào mảng `"required": [..., "region"]` và cập nhật trường `"description"` của `region` với hướng dẫn trích xuất rõ ràng: 'Mã vùng địa lý hai chữ cái (ví dụ: VN, US, JP) được trích xuất từ câu hỏi của người dùng; nếu người dùng không nhắc đến, mặc định sử dụng VN'.
+- Giả thuyết: 'Bằng việc đưa `region` vào danh sách tham số bắt buộc (required) và làm rõ mô tả trong schema của tool mà không thay đổi system prompt hay model, tỷ lệ các lời gọi tool thiếu đối số `region` khi người dùng đã cung cấp thông tin sẽ giảm từ 35% về dưới 1%.'
+2. Dự đoán phân loại các ca kiểm thử (Case Prediction):
+- Case thay đổi tích cực: Các câu hỏi người dùng có nhắc đến địa danh (ví dụ: 'Tìm khách sạn tại Đà Nẵng' hoặc 'Tra cứu tại Hà Nội') trước đây bị bỏ quên `region`, nay sẽ sinh đối số chính xác `region: 'VN'`.
+- Case không thay đổi: Các câu hỏi tra cứu chuẩn mực trước đây đã có đủ thông tin và sinh đúng `region` sẽ tiếp tục sinh đúng như cũ.
+3. Rủi ro hồi quy tiềm ẩn (Regression Risk):
+Khi `region` trở thành tham số bắt buộc trong schema, đối với các câu hỏi mà người dùng hoàn toàn KHÔNG cung cấp địa danh hoặc ngữ cảnh vùng (ví dụ: 'Tìm sách lập trình Python hay nhất'), mô hình có nguy cơ sinh ra giá trị `region` bịa đặt (hallucinated default) hoặc cố ép gán vùng địa lý không phù hợp cho các truy vấn toàn cầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Version Change Hypothesis yêu cầu cô lập biến số nghiên cứu bằng cách chỉ chỉnh sửa duy nhất một artifact tại một thời điểm. Điều này bảo toàn khả năng quy kết nguyên nhân (causal attribution), cho phép đo lường chính xác tác động của thay đổi đối với cả các ca cần sửa và rủi ro hồi quy phát sinh trên các ca biên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Function Calling &amp; Tool Definition Documentation &amp; Controlled Experimentation in Software Engineering (https://platform.openai.com/docs/guides/function-calling)</t>
         </is>
       </c>
     </row>
@@ -1558,10 +1708,28 @@
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết trước khi chạy: dùng/không dùng tool, đối số và hành động kỳ vọng.
-Phân tích theo nguyên lý thiết kế: Viết trước khi chạy: dùng/không dùng tool, đối số và hành động kỳ vọng.</t>
+- 1.0 điểm: Case 1 kiểm tra chính xác hành vi gọi tool đọc `lookup_course` khi người dùng hỏi thông tin.
+- 1.0 điểm: Case 2 kiểm tra chính xác hành vi gọi tool ghi `enroll_course` với đầy đủ tham số và xác nhận.
+- 1.0 điểm: Case 3 kiểm tra an toàn: không gọi tool ghi khi thiếu tham số, kích hoạt hỏi lại.
+- 1.0 điểm: Case 4 kiểm tra ranh giới: không gọi bất kỳ tool nào đối với hội thoại thông thường.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Bộ Smoke Test cố định gồm 4 test cases cho Agent khóa học:
+1. Case 1: Tra cứu thông tin khóa học (Read-only Happy Path)
+- Đầu vào: 'Cho tôi xem học phí và thời lượng của khóa học Kỹ thuật Prompt.'
+- Hành vi quan sát được kỳ vọng: Agent gọi đúng tool `lookup_course(course_name='Kỹ thuật Prompt')`; KHÔNG gọi tool `enroll_course`. Sau khi nhận kết quả, trả lời thông tin học phí và thời lượng đầy đủ cho người dùng.
+2. Case 2: Đăng ký khóa học đầy đủ thông tin (Write Action with Confirmation)
+- Đầu vào: 'Tôi muốn đăng ký học khóa Kỹ thuật Prompt, mã sinh viên của tôi là SV888, tôi xác nhận đăng ký.'
+- Hành vi quan sát được kỳ vọng: Agent gọi tool `enroll_course(student_id='SV888', course_name='Kỹ thuật Prompt')`. Sau khi tool trả về kết quả thành công, agent xuất thông báo đăng ký thành công kèm mã xác nhận.
+3. Case 3: Đăng ký nhưng thiếu thông tin bắt buộc (Safety &amp; Clarification Path)
+- Đầu vào: 'Tôi muốn đăng ký khóa học ngay bây giờ.'
+- Hành vi quan sát được kỳ vọng: Agent TUYỆT ĐỐI KHÔNG gọi `enroll_course` (ngăn chặn gọi tool với tham số rỗng/bịa); Agent phản hồi bằng câu hỏi yêu cầu người dùng cung cấp tên khóa học và mã sinh viên.
+4. Case 4: Hội thoại ngoài phạm vi / Chào hỏi xã giao (No-Tool Boundary Path)
+- Đầu vào: 'Xin chào, hôm nay bạn cảm thấy thế nào?'
+- Hành vi quan sát được kỳ vọng: Agent trả lời lịch sự bằng văn bản tự nhiên, KHÔNG gọi bất kỳ tool nào (`lookup_course` hay `enroll_course`).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một bộ Smoke Test cố định cho Tool-calling Agent phải bao phủ 4 hình thái hành vi cơ bản: gọi tool đọc, gọi tool ghi kèm xác nhận, xử lý thiếu dữ liệu (hỏi lại thay vì gọi ẩu), và từ chối gọi tool khi ngoài phạm vi. Các tiêu chí hành vi phải hoàn toàn quan sát được qua trace trước khi triển khai thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation - Testing &amp; Evaluating Agents &amp; Test-Driven Development for LLM Applications (https://python.langchain.com/docs/concepts/)</t>
         </is>
       </c>
     </row>
